--- a/analysis/regression_workbook.xlsx
+++ b/analysis/regression_workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BITSom\Assignments\Capstone Project\part3\Ajay_Undale_2511455_part3_regression_insights\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D53014-2619-40E4-846D-0FCD59E3C863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B2A36F-0950-4A65-A655-8118C9278DF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="805" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" tabRatio="805" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Original_Data" sheetId="1" r:id="rId1"/>
@@ -617,22 +617,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -47133,7 +47133,7 @@
       <c r="E12" s="4">
         <v>63.864872683367629</v>
       </c>
-      <c r="F12" s="10">
+      <c r="F12" s="9">
         <v>2.4800615101359601E-14</v>
       </c>
     </row>
@@ -47237,7 +47237,7 @@
       <c r="D18" s="5">
         <v>7.991550080138869</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="11">
         <v>2.4800615101360099E-14</v>
       </c>
       <c r="F18" s="5">
@@ -47448,8 +47448,8 @@
       <c r="D40" s="5">
         <v>29.796791372776362</v>
       </c>
-      <c r="E40" s="5">
-        <v>4.7503615090054677E-94</v>
+      <c r="E40" s="11">
+        <v>4.7503615090054699E-94</v>
       </c>
       <c r="F40" s="5">
         <v>33.322246825554025</v>
@@ -47466,6 +47466,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -47508,7 +47509,7 @@
         <v>124</v>
       </c>
       <c r="B5" s="4">
-        <v>0.84338181547547275</v>
+        <v>0.84338181547547297</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -47957,6 +47958,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -51576,10 +51578,10 @@
       <c r="F4" s="4">
         <v>2.1295753275898299</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="10">
         <v>2.4800615101359601E-14</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="10">
         <v>2.4800615101360099E-14</v>
       </c>
       <c r="I4" t="s">
@@ -51613,7 +51615,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="12" t="s">
         <v>158</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -51622,16 +51624,16 @@
       <c r="C6" s="13">
         <v>0.84338181547547275</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="12">
         <v>0.83831326581448495</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="12">
         <v>79854.166586721345</v>
       </c>
       <c r="F6" s="4">
         <v>6940.2736813955335</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G6" s="12">
         <v>5.1598243207349408E-118</v>
       </c>
       <c r="H6" s="4">
@@ -51639,65 +51641,65 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="9"/>
+      <c r="A7" s="12"/>
       <c r="B7" s="4" t="s">
         <v>119</v>
       </c>
       <c r="C7" s="13"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
       <c r="F7" s="4">
         <v>-24686.003142290148</v>
       </c>
-      <c r="G7" s="9"/>
+      <c r="G7" s="12"/>
       <c r="H7" s="4">
         <v>1.0429685891970007E-5</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="9"/>
+      <c r="A8" s="12"/>
       <c r="B8" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C8" s="13"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
       <c r="F8" s="4">
         <v>1.183722590602903</v>
       </c>
-      <c r="G8" s="9"/>
+      <c r="G8" s="12"/>
       <c r="H8" s="4">
         <v>9.4934457479485552E-20</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="9"/>
+      <c r="A9" s="12"/>
       <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="13"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
       <c r="F9" s="4">
         <v>27.485489731889228</v>
       </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="12"/>
       <c r="H9" s="4">
         <v>8.6522208000229166E-26</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="9"/>
+      <c r="A10" s="12"/>
       <c r="B10" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="13"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
       <c r="F10" s="4">
         <v>-65453.459550838423</v>
       </c>
-      <c r="G10" s="9"/>
+      <c r="G10" s="12"/>
       <c r="H10" s="4">
         <v>5.9435094126225947E-2</v>
       </c>
@@ -51706,81 +51708,81 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="9"/>
+      <c r="A11" s="12"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="13"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
       <c r="F11" s="4">
         <v>3430.0709089518359</v>
       </c>
-      <c r="G11" s="9"/>
+      <c r="G11" s="12"/>
       <c r="H11" s="4">
         <v>4.6704983531839538E-3</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="9"/>
+      <c r="A12" s="12"/>
       <c r="B12" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="13"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
       <c r="F12" s="4">
         <v>3113.1262629868256</v>
       </c>
-      <c r="G12" s="9"/>
+      <c r="G12" s="12"/>
       <c r="H12" s="4">
         <v>1.0716330496302334E-11</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="9"/>
+      <c r="A13" s="12"/>
       <c r="B13" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="13"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
       <c r="F13" s="4">
         <v>-3057.9603369914739</v>
       </c>
-      <c r="G13" s="9"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="4">
         <v>6.9359615385432747E-8</v>
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="9"/>
+      <c r="A14" s="12"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="13"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
       <c r="F14" s="4">
         <v>13480.924561135671</v>
       </c>
-      <c r="G14" s="9"/>
+      <c r="G14" s="12"/>
       <c r="H14" s="4">
         <v>3.4190995156286083E-2</v>
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="9"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="13"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
       <c r="F15" s="4">
         <v>12258.516462055735</v>
       </c>
-      <c r="G15" s="9"/>
+      <c r="G15" s="12"/>
       <c r="H15" s="4">
         <v>7.8991786374877047E-3</v>
       </c>
